--- a/INCREMENTO3/Excels/tabla de esfuerzo incremento3.xlsx
+++ b/INCREMENTO3/Excels/tabla de esfuerzo incremento3.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Felip\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\addan\OneDrive\Documentos\GitHub\ING-DE-SOFTWARE\INCREMENTO3\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AD99A948-A1B7-E84C-880C-C2400FDD439B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDEBB340-D816-458E-801E-4F2D85069E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B5DFA8D9-4F7C-4AFF-9769-0DB5C53111F2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B5DFA8D9-4F7C-4AFF-9769-0DB5C53111F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t xml:space="preserve">tareas pendientes </t>
   </si>
@@ -45,9 +48,6 @@
   </si>
   <si>
     <t>ACTIVIDADES</t>
-  </si>
-  <si>
-    <t>accediendo al menu</t>
   </si>
   <si>
     <t>El sistema debe generar el documento en formato PDF</t>
@@ -69,6 +69,18 @@
   </si>
   <si>
     <t>El sistema debe eliminar el permiso que se quiere eliminar de la base de datos</t>
+  </si>
+  <si>
+    <t>Imprimiendo informe de asistencia</t>
+  </si>
+  <si>
+    <t>Vizualizando informe diario de asistencia</t>
+  </si>
+  <si>
+    <t>Imprimiendo permisos</t>
+  </si>
+  <si>
+    <t>Eliminando permisos</t>
   </si>
 </sst>
 </file>
@@ -271,6 +283,3335 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Hoja1!$AA$63</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$AB$63</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B336-4E22-A7CC-2B0DFD51C49C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="332101728"/>
+        <c:axId val="332109888"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="332101728"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="332109888"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="332109888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="332101728"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-CL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="50000"/>
+                    <a:lumOff val="50000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-CL"/>
+              <a:t>Burn-Down INCREMENTO 3</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="2.1465780049729859E-2"/>
+          <c:y val="7.216874238830992E-2"/>
+          <c:w val="0.96417524443167735"/>
+          <c:h val="0.83833854223562032"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="stacked"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Esfuerzo Real Acumulado HH</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="flat" cmpd="dbl" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-1.0256411084709905E-3"/>
+                  <c:y val="1.5566188706025325E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-53FB-4149-A7B4-EDD71E14F7B8}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CL"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$Q$11:$X$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-53FB-4149-A7B4-EDD71E14F7B8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Esfuerzo Estimado Acumulado HH</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="flat" cmpd="dbl" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-7.179487759296407E-3"/>
+                  <c:y val="-5.0590113294582344E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-53FB-4149-A7B4-EDD71E14F7B8}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="2.0512822169417556E-3"/>
+                  <c:y val="-3.5023924588557021E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-53FB-4149-A7B4-EDD71E14F7B8}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="-2.3349283059038061E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-53FB-4149-A7B4-EDD71E14F7B8}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CL"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$Q$12:$X$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-53FB-4149-A7B4-EDD71E14F7B8}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1201153136"/>
+        <c:axId val="1201136816"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1201153136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                  <a:alpha val="32000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+            <a:tailEnd type="none" w="med" len="lg"/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1201136816"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1201136816"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                  <a:alpha val="32000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+            <a:tailEnd type="none" w="med" len="lg"/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1201153136"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:legendEntry>
+        <c:idx val="0"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="1"/>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1300" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:txPr>
+      </c:legendEntry>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.43753833535540765"/>
+          <c:y val="7.193524955771953E-2"/>
+          <c:w val="0.52287199861675737"/>
+          <c:h val="0.12039497058894275"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-CL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-CL"/>
+              <a:t>burn-UP</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="es-CL" baseline="0"/>
+              <a:t> INCREMENTO 3</a:t>
+            </a:r>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="2.5851720211867664E-2"/>
+          <c:y val="0.11928192182595976"/>
+          <c:w val="0.9546905448993106"/>
+          <c:h val="0.81654662101675213"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Esfuerzo Real Acumulado HH</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="diamond"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CL"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$AF$11:$AM$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9281-4381-919A-FEA2A1C73447}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Esfuerzo Estimado Acumulado HH</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="22225" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="square"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="50000"/>
+                        <a:lumOff val="50000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="es-CL"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:val>
+            <c:numRef>
+              <c:f>Hoja1!$AF$12:$AM$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>19</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9281-4381-919A-FEA2A1C73447}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="328816320"/>
+        <c:axId val="328833120"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="328816320"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="328833120"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="328833120"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="dk1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-CL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="328816320"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-CL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="lt1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-CL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="237">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+        <a:tailEnd type="none" w="med" len="lg"/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="38100" cap="flat" cmpd="dbl" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+            <a:alpha val="32000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+            <a:alpha val="32000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+        <a:tailEnd type="none" w="med" len="lg"/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="150" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="rnd"/>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+        <a:tailEnd type="none" w="med" len="lg"/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="239">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="800" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="22225" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" cap="all" spc="120" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="800" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>134287</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>150838</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>396615</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>83382</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BC9A43C4-76F9-5EE4-89BC-06FC0647893D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>390370</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>140533</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>562131</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>109304</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Gráfico 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C4EEE447-38D8-D4A8-8DE6-34CED69AA391}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>515286</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>15614</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>15614</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Gráfico 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E3E4061E-D4E1-F28F-218B-D23D14F8CA2F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="6">
+          <cell r="AL6">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="AL7">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="AL9">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="AL10">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="AL12">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="AL13">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="AL15">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="AL16">
+            <v>2</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
@@ -588,13 +3929,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0740A99-216B-4C42-A18C-D73C10A53F41}">
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultColWidth="10.76171875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AM19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="144.4765625" customWidth="1"/>
+    <col min="1" max="1" width="144.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B1" s="1">
         <v>45946</v>
       </c>
@@ -620,7 +3961,7 @@
         <v>45953</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -649,36 +3990,36 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C3" s="15">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D3" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E3" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F3" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3" s="15">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H3" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3" s="15">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
@@ -688,10 +4029,10 @@
       <c r="H4" s="13"/>
       <c r="I4" s="13"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>2</v>
       </c>
@@ -720,9 +4061,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B7" s="7">
         <v>0</v>
@@ -749,9 +4090,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="9">
         <v>2</v>
@@ -778,9 +4119,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="9">
         <v>2</v>
@@ -799,8 +4140,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="10"/>
+    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>11</v>
+      </c>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
@@ -814,27 +4157,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E11" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F11" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H11" s="7">
         <v>0</v>
@@ -842,10 +4185,58 @@
       <c r="I11" s="7">
         <v>0</v>
       </c>
+      <c r="Q11">
+        <v>16</v>
+      </c>
+      <c r="R11">
+        <v>16</v>
+      </c>
+      <c r="S11">
+        <v>12</v>
+      </c>
+      <c r="T11">
+        <v>12</v>
+      </c>
+      <c r="U11">
+        <v>12</v>
+      </c>
+      <c r="V11">
+        <v>12</v>
+      </c>
+      <c r="W11">
+        <v>9</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>9</v>
+      </c>
+      <c r="AH11">
+        <v>12</v>
+      </c>
+      <c r="AI11">
+        <v>12</v>
+      </c>
+      <c r="AJ11">
+        <v>12</v>
+      </c>
+      <c r="AK11">
+        <v>12</v>
+      </c>
+      <c r="AL11">
+        <v>16</v>
+      </c>
+      <c r="AM11">
+        <v>16</v>
+      </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="9">
         <v>2</v>
@@ -871,9 +4262,66 @@
       <c r="I12" s="7">
         <v>0</v>
       </c>
+      <c r="Q12">
+        <f>SUM([1]Sheet1!$AL$6:$AL$16)</f>
+        <v>19</v>
+      </c>
+      <c r="R12">
+        <f>SUM([1]Sheet1!$AL$6:$AL$16)</f>
+        <v>19</v>
+      </c>
+      <c r="S12">
+        <f>19-5</f>
+        <v>14</v>
+      </c>
+      <c r="T12">
+        <f t="shared" ref="T12:V12" si="0">19-5</f>
+        <v>14</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="W12">
+        <f>V12-5</f>
+        <v>9</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>9</v>
+      </c>
+      <c r="AH12">
+        <v>14</v>
+      </c>
+      <c r="AI12">
+        <v>14</v>
+      </c>
+      <c r="AJ12">
+        <v>14</v>
+      </c>
+      <c r="AK12">
+        <v>14</v>
+      </c>
+      <c r="AL12">
+        <v>19</v>
+      </c>
+      <c r="AM12">
+        <v>19</v>
+      </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="10"/>
+    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>12</v>
+      </c>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
@@ -885,9 +4333,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" s="9">
         <v>2</v>
@@ -914,37 +4362,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B15" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D15" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F15" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I15" s="7">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="10"/>
+    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
@@ -956,27 +4406,27 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B17" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C17" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F17" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H17" s="9">
         <v>3</v>
@@ -985,9 +4435,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B18" s="9">
         <v>2</v>
@@ -1014,35 +4464,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="17"/>
       <c r="B19" s="9">
         <f>SUM(B8:B18)</f>
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C19" s="9">
-        <f t="shared" ref="C19:H19" si="0">SUM(C8:C18)</f>
-        <v>19</v>
+        <f t="shared" ref="C19:H19" si="1">SUM(C8:C18)</f>
+        <v>16</v>
       </c>
       <c r="D19" s="9">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="E19" s="9">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="F19" s="9">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="G19" s="9">
-        <f t="shared" si="0"/>
-        <v>15</v>
+        <f t="shared" si="1"/>
+        <v>12</v>
       </c>
       <c r="H19" s="9">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f t="shared" si="1"/>
+        <v>9</v>
       </c>
       <c r="I19" s="7">
         <v>0</v>
@@ -1050,5 +4500,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>